--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.66197023349344</v>
+        <v>4.170070162942684</v>
       </c>
       <c r="D2" t="n">
-        <v>23.44332625275797</v>
+        <v>3.80954051607317</v>
       </c>
       <c r="E2" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F2" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.00904840037093</v>
+        <v>4.388970365060277</v>
       </c>
       <c r="D3" t="n">
-        <v>25.51867549563523</v>
+        <v>4.146784768040725</v>
       </c>
       <c r="E3" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F3" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.1304149310658</v>
+        <v>6.358692426298193</v>
       </c>
       <c r="D4" t="n">
-        <v>37.7377449606355</v>
+        <v>6.132383556103269</v>
       </c>
       <c r="E4" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F4" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.96657157529944</v>
+        <v>10.88206788098616</v>
       </c>
       <c r="D5" t="n">
-        <v>55.05976866097423</v>
+        <v>8.947212407408312</v>
       </c>
       <c r="E5" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F5" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.29484170585015</v>
+        <v>9.79791177720065</v>
       </c>
       <c r="D6" t="n">
-        <v>53.01842250576681</v>
+        <v>8.615493657187107</v>
       </c>
       <c r="E6" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F6" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.58110452818536</v>
+        <v>8.869429485830121</v>
       </c>
       <c r="D7" t="n">
-        <v>54.72421574540113</v>
+        <v>8.892685058627684</v>
       </c>
       <c r="E7" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F7" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.51926171128718</v>
+        <v>4.796880028084167</v>
       </c>
       <c r="D8" t="n">
-        <v>29.9656084950657</v>
+        <v>4.869411380448176</v>
       </c>
       <c r="E8" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F8" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72923732979359</v>
+        <v>5.806001066091459</v>
       </c>
       <c r="D9" t="n">
-        <v>35.8523011543728</v>
+        <v>5.825998937585581</v>
       </c>
       <c r="E9" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F9" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.6453672350179</v>
+        <v>2.054872175690409</v>
       </c>
       <c r="D10" t="n">
-        <v>12.06063620436262</v>
+        <v>1.959853383208926</v>
       </c>
       <c r="E10" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F10" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.3120774535255</v>
+        <v>5.900712586197894</v>
       </c>
       <c r="D11" t="n">
-        <v>35.61142497993859</v>
+        <v>5.786856559240021</v>
       </c>
       <c r="E11" t="n">
-        <v>16.13066886794616</v>
+        <v>2.621233691041251</v>
       </c>
       <c r="F11" t="n">
-        <v>13.72162622351377</v>
+        <v>2.229764261320987</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
